--- a/Trained-models/PCA eval graphs.xlsx
+++ b/Trained-models/PCA eval graphs.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0b86e2d661be6e75/Documents/School/UMGC/BIOT670I Capstone Course/REPO/Trained-models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAE07A32-F93D-4087-BDA2-576B3F82133A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="214" documentId="8_{DAE07A32-F93D-4087-BDA2-576B3F82133A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0DEDF21-BD96-493A-AC8F-A45721009891}"/>
   <bookViews>
-    <workbookView xWindow="12150" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{86558FDB-B793-4CDC-A254-DD65741D51FE}"/>
+    <workbookView xWindow="-16650" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{86558FDB-B793-4CDC-A254-DD65741D51FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="24">
   <si>
     <t>Accuracy</t>
   </si>
@@ -82,12 +83,39 @@
   <si>
     <t>PCA 10</t>
   </si>
+  <si>
+    <t>Validation Set Confusion Matrix</t>
+  </si>
+  <si>
+    <t>True Positives</t>
+  </si>
+  <si>
+    <t>False Positives</t>
+  </si>
+  <si>
+    <t>True Negatives</t>
+  </si>
+  <si>
+    <t>False Negatives</t>
+  </si>
+  <si>
+    <t>Test Set Confusion Matrix</t>
+  </si>
+  <si>
+    <t>PCA 40 percentage distribution</t>
+  </si>
+  <si>
+    <t>Total amount of negatives</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,13 +123,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="3" tint="0.749992370372631"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3" tint="0.749992370372631"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -116,17 +178,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -294,7 +362,7 @@
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -320,9 +388,6 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$B$2:$G$2</c:f>
@@ -406,9 +471,6 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$B$2:$G$2</c:f>
@@ -492,9 +554,6 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$B$2:$G$2</c:f>
@@ -578,9 +637,6 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$B$2:$G$2</c:f>
@@ -664,9 +720,6 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$B$2:$G$2</c:f>
@@ -728,14 +781,13 @@
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
         <c:axId val="414429615"/>
         <c:axId val="414430575"/>
       </c:barChart>
@@ -1118,6 +1170,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="584424207"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -1273,7 +1326,7 @@
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1699,7 +1752,6 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
         <c:axId val="582972415"/>
         <c:axId val="582971455"/>
       </c:barChart>
@@ -2079,6 +2131,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="616145599"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -3290,16 +3343,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
+      <xdr:rowOff>100012</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3349,6 +3402,10 @@
 </FeaturePropertyBags>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{43EF4665-B1BE-410B-9F1D-0FDC2A1A283D}" name="Table1" displayName="Table1" ref="A2:G8" totalsRowShown="0">
   <autoFilter ref="A2:G8" xr:uid="{43EF4665-B1BE-410B-9F1D-0FDC2A1A283D}"/>
@@ -3366,16 +3423,44 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AC467B24-8FE4-476E-9C76-7247D924C92C}" name="Table2" displayName="Table2" ref="I2:O8" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AC467B24-8FE4-476E-9C76-7247D924C92C}" name="Table2" displayName="Table2" ref="I2:O8" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="I2:O8" xr:uid="{AC467B24-8FE4-476E-9C76-7247D924C92C}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{44E9CBAF-4134-4EEC-85AF-E84FB1E8A41A}" name="SCORES" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{DB4EE74C-A6D4-44D4-B434-3BE4BD1BD32C}" name="PCA 64" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{BA1B3766-B0FC-4025-A027-560E84028D7C}" name="PCA 50" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{50C2FD1F-33D6-4F91-9263-325E7EE30CCB}" name="PCA 40" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{66CBA766-D30C-4246-AEE2-0B417E5A5CC0}" name="PCA 25" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{BC871FD5-BBCC-44E9-9631-ADFA1822F1CE}" name="PCA 10" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{A2194C3B-16DA-4C70-AE3C-8EED8D7F087B}" name="PCA 2" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{44E9CBAF-4134-4EEC-85AF-E84FB1E8A41A}" name="SCORES" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{DB4EE74C-A6D4-44D4-B434-3BE4BD1BD32C}" name="PCA 64" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{BA1B3766-B0FC-4025-A027-560E84028D7C}" name="PCA 50" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{50C2FD1F-33D6-4F91-9263-325E7EE30CCB}" name="PCA 40" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{66CBA766-D30C-4246-AEE2-0B417E5A5CC0}" name="PCA 25" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{BC871FD5-BBCC-44E9-9631-ADFA1822F1CE}" name="PCA 10" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{A2194C3B-16DA-4C70-AE3C-8EED8D7F087B}" name="PCA 2" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8109EEDB-84E6-4001-B817-1A10CE4DA006}" name="Table146" displayName="Table146" ref="A31:E37" totalsRowShown="0">
+  <autoFilter ref="A31:E37" xr:uid="{8109EEDB-84E6-4001-B817-1A10CE4DA006}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{A37E689F-7063-4826-AA05-1FA62024E02B}" name="SCORES"/>
+    <tableColumn id="2" xr3:uid="{518E89B4-AA3F-4697-80ED-3A5EB93740BC}" name="True Positives"/>
+    <tableColumn id="3" xr3:uid="{2CE59322-CE7E-4035-88A6-B3C0E520471E}" name="False Positives"/>
+    <tableColumn id="4" xr3:uid="{310CDF60-814C-4277-9D82-0E78210F4763}" name="True Negatives"/>
+    <tableColumn id="5" xr3:uid="{9BA7D505-DE21-427B-BBF7-EA7316A4A27B}" name="False Negatives"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7127191D-EA31-4974-B585-E65996A29C81}" name="Table1467" displayName="Table1467" ref="I31:M37" totalsRowShown="0">
+  <autoFilter ref="I31:M37" xr:uid="{7127191D-EA31-4974-B585-E65996A29C81}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{2C9FA167-DD00-4E74-81EA-224F931D2F4F}" name="SCORES"/>
+    <tableColumn id="2" xr3:uid="{A382C0B6-2CD3-41E3-938D-79B9B93A8A41}" name="True Positives"/>
+    <tableColumn id="3" xr3:uid="{D5136BFC-ED20-423C-8A89-A8618598ADB6}" name="False Positives"/>
+    <tableColumn id="4" xr3:uid="{1C7C265D-718D-4B13-9F67-AE3369AC9CE8}" name="True Negatives"/>
+    <tableColumn id="5" xr3:uid="{675FDA37-CD24-4E7B-999A-15F33132B920}" name="False Negatives"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3698,7 +3783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DCC85C2-2EDB-454D-8ADD-270B8EA360B9}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -3709,24 +3794,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -3750,25 +3835,25 @@
       <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3794,25 +3879,25 @@
       <c r="G3">
         <v>0.61899999999999999</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>0.71279999999999999</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="1">
         <v>0.71189999999999998</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="1">
         <v>0.70960000000000001</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="1">
         <v>0.69940000000000002</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="1">
         <v>0.70130000000000003</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="1">
         <v>0.68430000000000002</v>
       </c>
     </row>
@@ -3838,25 +3923,25 @@
       <c r="G4">
         <v>0.67549999999999999</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <v>0.68510000000000004</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="1">
         <v>0.68410000000000004</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="1">
         <v>0.68269999999999997</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="1">
         <v>0.67330000000000001</v>
       </c>
-      <c r="N4" s="2">
+      <c r="N4" s="1">
         <v>0.68389999999999995</v>
       </c>
-      <c r="O4" s="2">
+      <c r="O4" s="1">
         <v>0.6694</v>
       </c>
     </row>
@@ -3882,25 +3967,25 @@
       <c r="G5">
         <v>0.56440000000000001</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>0.83599999999999997</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="1">
         <v>0.83599999999999997</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="1">
         <v>0.83250000000000002</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="1">
         <v>0.82809999999999995</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="1">
         <v>0.79910000000000003</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5" s="1">
         <v>0.78510000000000002</v>
       </c>
     </row>
@@ -3926,25 +4011,25 @@
       <c r="G6">
         <v>0.61499999999999999</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>0.75309999999999999</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="1">
         <v>0.75249999999999995</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="1">
         <v>0.75019999999999998</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="1">
         <v>0.74270000000000003</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="1">
         <v>0.73709999999999998</v>
       </c>
-      <c r="O6" s="2">
+      <c r="O6" s="1">
         <v>0.72260000000000002</v>
       </c>
     </row>
@@ -3970,25 +4055,25 @@
       <c r="G7">
         <v>0.67210000000000003</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <v>0.79930000000000001</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="1">
         <v>0.79930000000000001</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="1">
         <v>0.79949999999999999</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="1">
         <v>0.78959999999999997</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="1">
         <v>0.76</v>
       </c>
-      <c r="O7" s="2">
+      <c r="O7" s="1">
         <v>0.76719999999999999</v>
       </c>
     </row>
@@ -4020,44 +4105,378 @@
         <f t="shared" si="0"/>
         <v>3.1459999999999999</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <f>SUM(J3:J7)</f>
         <v>3.7862999999999998</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="1">
         <f t="shared" ref="K8:O8" si="1">SUM(K3:K7)</f>
         <v>3.7837999999999998</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="1">
         <f t="shared" si="1"/>
         <v>3.7745000000000002</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="1">
         <f t="shared" si="1"/>
         <v>3.7331000000000003</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="1">
         <f t="shared" si="1"/>
         <v>3.6814</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O8" s="1">
         <f t="shared" si="1"/>
         <v>3.6285999999999996</v>
       </c>
     </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="I30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="O30">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" t="s">
+        <v>5</v>
+      </c>
+      <c r="J31" t="s">
+        <v>16</v>
+      </c>
+      <c r="K31" t="s">
+        <v>17</v>
+      </c>
+      <c r="L31" t="s">
+        <v>18</v>
+      </c>
+      <c r="M31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32">
+        <v>798</v>
+      </c>
+      <c r="C32">
+        <v>289</v>
+      </c>
+      <c r="D32">
+        <v>714</v>
+      </c>
+      <c r="E32">
+        <v>375</v>
+      </c>
+      <c r="I32" t="s">
+        <v>6</v>
+      </c>
+      <c r="J32">
+        <v>953</v>
+      </c>
+      <c r="K32">
+        <v>438</v>
+      </c>
+      <c r="L32">
+        <v>598</v>
+      </c>
+      <c r="M32">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33">
+        <v>798</v>
+      </c>
+      <c r="C33">
+        <v>289</v>
+      </c>
+      <c r="D33">
+        <v>714</v>
+      </c>
+      <c r="E33">
+        <v>375</v>
+      </c>
+      <c r="I33" t="s">
+        <v>9</v>
+      </c>
+      <c r="J33">
+        <v>953</v>
+      </c>
+      <c r="K33">
+        <v>440</v>
+      </c>
+      <c r="L33">
+        <v>596</v>
+      </c>
+      <c r="M33">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34">
+        <v>799</v>
+      </c>
+      <c r="C34">
+        <v>291</v>
+      </c>
+      <c r="D34">
+        <v>712</v>
+      </c>
+      <c r="E34">
+        <v>374</v>
+      </c>
+      <c r="I34" t="s">
+        <v>10</v>
+      </c>
+      <c r="J34">
+        <v>949</v>
+      </c>
+      <c r="K34">
+        <v>441</v>
+      </c>
+      <c r="L34">
+        <v>595</v>
+      </c>
+      <c r="M34">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35">
+        <v>783</v>
+      </c>
+      <c r="C35">
+        <v>281</v>
+      </c>
+      <c r="D35">
+        <v>722</v>
+      </c>
+      <c r="E35">
+        <v>390</v>
+      </c>
+      <c r="I35" t="s">
+        <v>11</v>
+      </c>
+      <c r="J35">
+        <v>944</v>
+      </c>
+      <c r="K35">
+        <v>458</v>
+      </c>
+      <c r="L35">
+        <v>578</v>
+      </c>
+      <c r="M35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36">
+        <v>709</v>
+      </c>
+      <c r="C36">
+        <v>293</v>
+      </c>
+      <c r="D36">
+        <v>710</v>
+      </c>
+      <c r="E36">
+        <v>464</v>
+      </c>
+      <c r="I36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36">
+        <v>911</v>
+      </c>
+      <c r="K36">
+        <v>421</v>
+      </c>
+      <c r="L36">
+        <v>615</v>
+      </c>
+      <c r="M36">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37">
+        <v>662</v>
+      </c>
+      <c r="C37">
+        <v>318</v>
+      </c>
+      <c r="D37">
+        <v>685</v>
+      </c>
+      <c r="E37">
+        <v>511</v>
+      </c>
+      <c r="I37" t="s">
+        <v>11</v>
+      </c>
+      <c r="J37">
+        <v>895</v>
+      </c>
+      <c r="K37">
+        <v>442</v>
+      </c>
+      <c r="L37">
+        <v>594</v>
+      </c>
+      <c r="M37">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I39" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39">
+        <f>(J34/2176)*100</f>
+        <v>43.612132352941174</v>
+      </c>
+      <c r="K39">
+        <f t="shared" ref="K39:M39" si="2">(K34/2176)*100</f>
+        <v>20.266544117647058</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="2"/>
+        <v>27.34375</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="2"/>
+        <v>8.7775735294117645</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I41" t="s">
+        <v>22</v>
+      </c>
+      <c r="J41">
+        <f>SUM(K34,L34)</f>
+        <v>1036</v>
+      </c>
+      <c r="K41">
+        <f>(J41/O30)*100</f>
+        <v>47.610294117647058</v>
+      </c>
+      <c r="L41">
+        <f>(K34/J41)*100</f>
+        <v>42.567567567567565</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J42">
+        <f>SUM(K32:L32)</f>
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I43" t="s">
+        <v>23</v>
+      </c>
+      <c r="K43">
+        <f>AVERAGE(Table1467[False Positives])</f>
+        <v>440</v>
+      </c>
+      <c r="L43">
+        <f>(K43/O30)*100</f>
+        <v>20.22058823529412</v>
+      </c>
+      <c r="M43">
+        <f>(K43/J42)*100</f>
+        <v>42.471042471042466</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="I30:M30"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="B32:B37 D32:D37 J32:J37 L32:L37">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color theme="9" tint="0.79998168889431442"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <color theme="9" tint="-0.249977111117893"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32:C37 E32:E37 K32:K37 M32:M37">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color theme="5" tint="0.59999389629810485"/>
+        <color theme="5" tint="0.39997558519241921"/>
+        <color theme="5" tint="-0.249977111117893"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <tableParts count="2">
-    <tablePart r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <tableParts count="4">
     <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>